--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>113263.3</v>
+        <v>125978.25</v>
       </c>
       <c r="S7" t="n">
         <v>5651</v>
@@ -1336,7 +1336,7 @@
         <v>5651</v>
       </c>
       <c r="U7" t="n">
-        <v>113263.3</v>
+        <v>125978.25</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>293917.71</v>
+        <v>298214.01</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4389,10 +4389,10 @@
         <v>17186912.55</v>
       </c>
       <c r="S30" t="n">
-        <v>16575976.04</v>
+        <v>16576136.27</v>
       </c>
       <c r="T30" t="n">
-        <v>16582548.69</v>
+        <v>16582708.92</v>
       </c>
       <c r="U30" t="n">
         <v>17183752.13</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="X53" t="n">
         <v>100000</v>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -7593,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="X54" t="n">
         <v>50000</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="X56" t="n">
         <v>50000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="X60" t="n">
         <v>70000</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>244900</v>
+        <v>367350</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -9177,10 +9177,10 @@
         <v>921519</v>
       </c>
       <c r="S66" t="n">
-        <v>244900</v>
+        <v>367350</v>
       </c>
       <c r="T66" t="n">
-        <v>244900</v>
+        <v>367350</v>
       </c>
       <c r="U66" t="n">
         <v>921519</v>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -10120,7 +10120,7 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="X73" t="n">
         <v>100000</v>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -10386,7 +10386,7 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="X75" t="n">
         <v>75000</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2092306.37</v>
+        <v>2795073.05</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1576800</v>
+        <v>2366800</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -15960,10 +15960,10 @@
         <v>8578400</v>
       </c>
       <c r="S117" t="n">
-        <v>1576800</v>
+        <v>2366800</v>
       </c>
       <c r="T117" t="n">
-        <v>2356400</v>
+        <v>3146400</v>
       </c>
       <c r="U117" t="n">
         <v>8578400</v>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16072,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>5478096.41</v>
+        <v>9099111.57</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -17284,7 +17284,7 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -17302,7 +17302,7 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="X127" t="n">
         <v>75000</v>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18215,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="X134" t="n">
         <v>75000</v>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18614,7 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>55747.3</v>
+        <v>127873.65</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>27873.65</v>
+        <v>100000</v>
       </c>
       <c r="X137" t="n">
         <v>100000</v>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>41561876.54</v>
+        <v>45947180.23</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -19796,7 +19796,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>7288668.99</v>
+        <v>9693904.550000001</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -19817,10 +19817,10 @@
         <v>80380048.28</v>
       </c>
       <c r="S146" t="n">
-        <v>33044222.28</v>
+        <v>33050672.28</v>
       </c>
       <c r="T146" t="n">
-        <v>33044222.28</v>
+        <v>33050672.28</v>
       </c>
       <c r="U146" t="n">
         <v>79443026</v>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>15284010.55</v>
+        <v>17678768.73</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>02/03/2026 15:04:11</t>
+          <t>03/03/2026 09:35:52</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2893 - Realização do projeto "Vidas no trecho". Organização: Associação Rede Rua</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E308 - Formação para Grupos em Situação de Vulnerabilidade em Práticas Artísticas, Educacionais, Esp</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E309 - Formação para Grupos em Situação de Vulnerabilidade em Práticas Artísticas, Educacionais, Esp</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E310 - Formação para Grupos em Situação de Vulnerabilidade em Práticas Artísticas, Educacionais, Esp</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E311 - Ação social para Grupos em Situação de Vulnerabilidade. MRSC</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E313 - Formação para Grupos em Situação de Vulnerabilidade em Práticas Artísticas, Educacionais, Esp</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E314 - Realização de Eventos de Cultura, Esporte e Lazer na Periferia de São Paulo</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E319 - Formação para Grupos em Situação de Vulnerabilidade em Práticas Artísticas, Educacionais, Esp</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E141 - Implantação de Cozinha Industrial na Paróquia São João do Braz para Atendimento Social</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E120 - Atendimento Odontológico Gratuito</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2902 - Realização do projeto "Sábios em Ação". Organização: Instituto Mario Américo – IMA</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E302 - Formação para Grupos de Terceira Idade em Práticas Artísticas, Educacionais, Esportivas - UNI</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E318 - Formação para Grupos de Terceira Idade em Práticas Artísticas, Educacionais, Esportivas - GAR</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2897 - Realização do projeto "Formação no Enfrentamento à Violência Contra as Mulheres". Organizaçã</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2913 - Realização do Projeto "Formação para todas as Cidadãs Cantantes". Organização: Associação SO</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E312 - Formação para Grupos em Mulheres em Práticas Artísticas, Educacionais, Esportivas - Arandu</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2884 - Realização do Projeto "Histórias na Barra da Saia". Organização: Anderson Henrique de Olivei</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t xml:space="preserve">E2873 - Realização do Projeto "Observatório Indígena"- Organização: Aliança Universidade e os Povos </t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>03/03/2026 09:35:52</t>
+          <t>03/03/2026 11:48:33</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>125978.25</v>
+        <v>133308.41</v>
       </c>
       <c r="S7" t="n">
         <v>5651</v>
@@ -1336,7 +1336,7 @@
         <v>5651</v>
       </c>
       <c r="U7" t="n">
-        <v>125978.25</v>
+        <v>133308.41</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>33633.63</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>298214.01</v>
+        <v>301272.61</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>190046.21</v>
+        <v>194146.21</v>
       </c>
       <c r="P10" t="n">
         <v>566386.21</v>
@@ -1726,16 +1726,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>11915477.34</v>
+        <v>11919075.67</v>
       </c>
       <c r="S10" t="n">
-        <v>7409380.19</v>
+        <v>7724728.83</v>
       </c>
       <c r="T10" t="n">
-        <v>7423169.08</v>
+        <v>7738517.72</v>
       </c>
       <c r="U10" t="n">
-        <v>11349091.13</v>
+        <v>11352689.46</v>
       </c>
       <c r="V10" t="n">
         <v>13788.89</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>107.79</v>
+        <v>1011.1</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2651,25 +2651,25 @@
         <v>124658.62</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>14849.99</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1781472.96</v>
+        <v>1805858.93</v>
       </c>
       <c r="S17" t="n">
-        <v>1781472.96</v>
+        <v>1766622.97</v>
       </c>
       <c r="T17" t="n">
         <v>1781472.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1781472.96</v>
+        <v>1791008.94</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>14849.99</v>
       </c>
       <c r="W17" t="n">
         <v>1800000</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -3848,13 +3848,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>26530.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>277242.74</v>
+        <v>301236.74</v>
       </c>
       <c r="S26" t="n">
         <v>250712.54</v>
@@ -3863,7 +3863,7 @@
         <v>250712.54</v>
       </c>
       <c r="U26" t="n">
-        <v>277242.74</v>
+        <v>274706.54</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>157713.7</v>
+        <v>157814.59</v>
       </c>
       <c r="P28" t="n">
         <v>201875.44</v>
@@ -4123,10 +4123,10 @@
         <v>2035080.12</v>
       </c>
       <c r="S28" t="n">
-        <v>1485288.62</v>
+        <v>1485786</v>
       </c>
       <c r="T28" t="n">
-        <v>1597671.75</v>
+        <v>1598169.13</v>
       </c>
       <c r="U28" t="n">
         <v>1833204.68</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>438842.16</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4389,10 +4389,10 @@
         <v>17186912.55</v>
       </c>
       <c r="S30" t="n">
-        <v>16576136.27</v>
+        <v>16771112.95</v>
       </c>
       <c r="T30" t="n">
-        <v>16582708.92</v>
+        <v>16777685.6</v>
       </c>
       <c r="U30" t="n">
         <v>17183752.13</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>275631.58</v>
+        <v>275797.2</v>
       </c>
       <c r="P34" t="n">
         <v>2931914.44</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2034382.45</v>
+        <v>2870692.14</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>22178.9</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>245581.64</v>
+        <v>477352.94</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>6526.27</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2795073.05</v>
+        <v>3487177.25</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1308418.2</v>
+        <v>2080380.53</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>6526.27</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>28705.17</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1059.33</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2028.89</v>
+        <v>2985.29</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>84841.47</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>6470104.18</v>
+        <v>9705156.27</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>45947180.23</v>
+        <v>47043339.48</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -19681,7 +19681,7 @@
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>58907113.6</v>
+        <v>166342578.8</v>
       </c>
       <c r="S145" t="n">
         <v>29453556.8</v>
@@ -19690,7 +19690,7 @@
         <v>29453556.8</v>
       </c>
       <c r="U145" t="n">
-        <v>29453556.8</v>
+        <v>136889022</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -19805,7 +19805,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>2754000</v>
+        <v>3744000</v>
       </c>
       <c r="P146" t="n">
         <v>937022.28</v>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>
@@ -20736,7 +20736,7 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>10622477.2</v>
+        <v>12202659.89</v>
       </c>
       <c r="P153" t="n">
         <v>3068431.98</v>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>03/03/2026 11:48:33</t>
+          <t>04/03/2026 07:00:28</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI153"/>
+  <dimension ref="A1:AI154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -789,25 +789,25 @@
         <v>1443170.97</v>
       </c>
       <c r="P3" t="n">
-        <v>21963.73</v>
+        <v>220570.58</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5587041.95</v>
+        <v>5729936.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4944239.18</v>
+        <v>5163175.63</v>
       </c>
       <c r="T3" t="n">
-        <v>4944239.18</v>
+        <v>5374434.98</v>
       </c>
       <c r="U3" t="n">
-        <v>5565078.22</v>
+        <v>5509365.67</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>211259.35</v>
       </c>
       <c r="W3" t="n">
         <v>16580488</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -1717,16 +1717,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>194146.21</v>
+        <v>251299.99</v>
       </c>
       <c r="P10" t="n">
-        <v>566386.21</v>
+        <v>1195004.56</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>11919075.67</v>
+        <v>12547694.02</v>
       </c>
       <c r="S10" t="n">
         <v>7724728.83</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>34774.81</v>
       </c>
       <c r="P19" t="n">
         <v>2750000</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
         <v>2035080.12</v>
       </c>
       <c r="S28" t="n">
-        <v>1485786</v>
+        <v>1484749.4</v>
       </c>
       <c r="T28" t="n">
         <v>1598169.13</v>
@@ -4132,7 +4132,7 @@
         <v>1833204.68</v>
       </c>
       <c r="V28" t="n">
-        <v>112383.13</v>
+        <v>113419.73</v>
       </c>
       <c r="W28" t="n">
         <v>1841736</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>47624.92</v>
+        <v>162275.63</v>
       </c>
       <c r="P30" t="n">
         <v>3160.42</v>
@@ -4386,16 +4386,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>17186912.55</v>
+        <v>17193479.55</v>
       </c>
       <c r="S30" t="n">
-        <v>16771112.95</v>
+        <v>16777679.95</v>
       </c>
       <c r="T30" t="n">
-        <v>16777685.6</v>
+        <v>16784252.6</v>
       </c>
       <c r="U30" t="n">
-        <v>17183752.13</v>
+        <v>17190319.13</v>
       </c>
       <c r="V30" t="n">
         <v>6572.65</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2564.77</v>
+        <v>38322.58</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -10906,10 +10906,10 @@
         <v>416595.36</v>
       </c>
       <c r="S79" t="n">
-        <v>327600</v>
+        <v>339609.47</v>
       </c>
       <c r="T79" t="n">
-        <v>327600</v>
+        <v>339609.47</v>
       </c>
       <c r="U79" t="n">
         <v>392752</v>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -13962,16 +13962,16 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>7686397.08</v>
+        <v>7692964.08</v>
       </c>
       <c r="S102" t="n">
-        <v>732972.62</v>
+        <v>739539.62</v>
       </c>
       <c r="T102" t="n">
-        <v>732972.62</v>
+        <v>739539.62</v>
       </c>
       <c r="U102" t="n">
-        <v>7686397.08</v>
+        <v>7692964.08</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2985.29</v>
+        <v>116985.29</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>4782427.07</v>
+        <v>5027120.48</v>
       </c>
       <c r="P118" t="n">
         <v>1425517.51</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16205,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>43983</v>
+        <v>62133</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>24906.96</v>
       </c>
       <c r="P122" t="n">
         <v>743505.8100000001</v>
@@ -16622,16 +16622,16 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3251361.85</v>
+        <v>3258804.45</v>
       </c>
       <c r="S122" t="n">
-        <v>1951991.24</v>
+        <v>1959433.84</v>
       </c>
       <c r="T122" t="n">
-        <v>1951991.24</v>
+        <v>1959433.84</v>
       </c>
       <c r="U122" t="n">
-        <v>2507856.04</v>
+        <v>2515298.64</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19235,13 +19235,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F142" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G142" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47043339.48</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -19273,43 +19273,43 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>40816540.35</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>20385904.54</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>157005102.66</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>118116606.21</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>123556318.6</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>136619198.12</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>166077092</v>
+        <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -19322,7 +19322,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19383,21 +19383,21 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>50457592.76</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -19406,43 +19406,43 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>40909913.71</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>20385904.54</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>157005102.66</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>118116606.21</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>123556318.6</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>136619198.12</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W143" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="X143" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -19460,22 +19460,22 @@
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19521,12 +19521,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -19563,10 +19563,10 @@
         <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X144" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
@@ -19575,7 +19575,7 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG144" t="inlineStr">
@@ -19603,12 +19603,12 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19649,21 +19649,21 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>12793490.4</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -19672,43 +19672,43 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>166342578.8</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="X145" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="Y145" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -19726,22 +19726,22 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -19796,7 +19796,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>9693904.550000001</v>
+        <v>17330633.4</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -19805,43 +19805,43 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>3744000</v>
+        <v>7871540.4</v>
       </c>
       <c r="P146" t="n">
-        <v>937022.28</v>
+        <v>29453556.8</v>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>80380048.28</v>
+        <v>166342578.8</v>
       </c>
       <c r="S146" t="n">
-        <v>33050672.28</v>
+        <v>29453556.8</v>
       </c>
       <c r="T146" t="n">
-        <v>33050672.28</v>
+        <v>29453556.8</v>
       </c>
       <c r="U146" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="X146" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="Y146" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Z146" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>82235403</v>
+        <v>141616875</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -19920,16 +19920,16 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>10114210.09</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -19938,43 +19938,43 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>4042120.9</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>937022.28</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>80380048.28</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>33050672.28</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>33050672.28</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="X147" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA147" t="n">
-        <v>2000</v>
+        <v>82235403</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
@@ -20002,12 +20002,12 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -20048,27 +20048,27 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -20080,25 +20080,25 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="X148" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y148" t="n">
         <v>0</v>
@@ -20107,7 +20107,7 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -20125,34 +20125,34 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -20166,22 +20166,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F149" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G149" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -20195,16 +20195,16 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -20213,25 +20213,25 @@
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S149" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U149" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="X149" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
         <v>0</v>
@@ -20240,7 +20240,7 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -20248,12 +20248,12 @@
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -20314,7 +20314,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -20361,10 +20361,10 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X150" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="Y150" t="n">
         <v>0</v>
@@ -20373,7 +20373,7 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -20432,22 +20432,22 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F151" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G151" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -20494,10 +20494,10 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X151" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="Y151" t="n">
         <v>0</v>
@@ -20506,7 +20506,7 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -20514,12 +20514,12 @@
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -20529,7 +20529,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -20565,22 +20565,22 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F152" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G152" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -20627,10 +20627,10 @@
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X152" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y152" t="n">
         <v>0</v>
@@ -20639,7 +20639,7 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -20647,12 +20647,12 @@
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -20662,17 +20662,17 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>04/03/2026 07:00:28</t>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>
@@ -20718,16 +20718,16 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>17678768.73</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -20736,34 +20736,34 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>12202659.89</v>
+        <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>35448208.44</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>32116802.57</v>
+        <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>33729566.67</v>
+        <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>32379776.46</v>
+        <v>0</v>
       </c>
       <c r="V153" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X153" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="Y153" t="n">
         <v>0</v>
@@ -20772,7 +20772,7 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -20790,22 +20790,155 @@
       </c>
       <c r="AF153" t="inlineStr">
         <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>05/03/2026 07:00:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>422</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G154" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>18235012.8</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>13797559.25</v>
+      </c>
+      <c r="P154" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>35448208.44</v>
+      </c>
+      <c r="S154" t="n">
+        <v>32116802.57</v>
+      </c>
+      <c r="T154" t="n">
+        <v>33729566.67</v>
+      </c>
+      <c r="U154" t="n">
+        <v>32379776.46</v>
+      </c>
+      <c r="V154" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W154" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X154" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG153" t="inlineStr">
+      <c r="AG154" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH153" t="inlineStr">
+      <c r="AH154" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>04/03/2026 07:00:28</t>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>05/03/2026 07:00:37</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI154"/>
+  <dimension ref="A1:AI155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1931102.91</v>
+        <v>2578031.81</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1443170.97</v>
+        <v>1844144.91</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -1454,25 +1454,25 @@
         <v>11257.26</v>
       </c>
       <c r="P8" t="n">
-        <v>161083.4</v>
+        <v>181083.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>403170.4</v>
+        <v>423170.4</v>
       </c>
       <c r="S8" t="n">
         <v>191768.25</v>
       </c>
       <c r="T8" t="n">
-        <v>191768.25</v>
+        <v>211768.25</v>
       </c>
       <c r="U8" t="n">
         <v>242087</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="W8" t="n">
         <v>242087</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12547694.02</v>
+        <v>12563981.41</v>
       </c>
       <c r="S10" t="n">
         <v>7724728.83</v>
@@ -1735,7 +1735,7 @@
         <v>7738517.72</v>
       </c>
       <c r="U10" t="n">
-        <v>11352689.46</v>
+        <v>11368976.85</v>
       </c>
       <c r="V10" t="n">
         <v>13788.89</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>34774.81</v>
+        <v>40389.32</v>
       </c>
       <c r="P19" t="n">
         <v>2750000</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4114,22 +4114,22 @@
         <v>157814.59</v>
       </c>
       <c r="P28" t="n">
-        <v>201875.44</v>
+        <v>202912.04</v>
       </c>
       <c r="Q28" t="n">
         <v>9180</v>
       </c>
       <c r="R28" t="n">
-        <v>2035080.12</v>
+        <v>2037299.69</v>
       </c>
       <c r="S28" t="n">
-        <v>1484749.4</v>
+        <v>1486549.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1598169.13</v>
+        <v>1599969.13</v>
       </c>
       <c r="U28" t="n">
-        <v>1833204.68</v>
+        <v>1834387.65</v>
       </c>
       <c r="V28" t="n">
         <v>113419.73</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>162275.63</v>
+        <v>374845.23</v>
       </c>
       <c r="P30" t="n">
         <v>3160.42</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>328</v>
+        <v>1441.7</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3430</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -9833,13 +9833,13 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1103.06</v>
+        <v>1495.27</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>257297.72</v>
+        <v>257689.93</v>
       </c>
       <c r="S71" t="n">
         <v>132420.68</v>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14488,13 +14488,13 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>216553.88</v>
+        <v>217702.09</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>453625.94</v>
+        <v>454774.15</v>
       </c>
       <c r="S106" t="n">
         <v>230854</v>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>98641.25</v>
+        <v>143942.4</v>
       </c>
       <c r="S111" t="n">
         <v>33311.56</v>
@@ -15168,7 +15168,7 @@
         <v>33311.56</v>
       </c>
       <c r="U111" t="n">
-        <v>98641.25</v>
+        <v>143942.4</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -15419,13 +15419,13 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>1621398.15</v>
+        <v>1802762.74</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>5048635.3</v>
+        <v>5230012.69</v>
       </c>
       <c r="S113" t="n">
         <v>2659928.13</v>
@@ -15434,7 +15434,7 @@
         <v>2660248.13</v>
       </c>
       <c r="U113" t="n">
-        <v>3427237.15</v>
+        <v>3427249.95</v>
       </c>
       <c r="V113" t="n">
         <v>320</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16072,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>9099111.57</v>
+        <v>9425812.26</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -18768,16 +18768,16 @@
         <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
         <v>5</v>
@@ -18800,58 +18800,58 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Amanda Vettorazzo</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F139" t="n">
         <v>4010</v>
       </c>
       <c r="G139" t="n">
-        <v>4302</v>
+        <v>4426</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>9705156.27</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -18874,7 +18874,7 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>6470104.18</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -18883,34 +18883,34 @@
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AB139" t="n">
         <v>5</v>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -18998,7 +18998,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>9705156.27</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -19007,7 +19007,7 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>6470104.18</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -19016,34 +19016,34 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="X140" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="Y140" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -19098,21 +19098,21 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F141" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G141" t="n">
-        <v>3002</v>
+        <v>4302</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -19164,19 +19164,19 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="X141" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AB141" t="n">
         <v>5</v>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>44906100</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -19297,10 +19297,10 @@
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
@@ -19309,7 +19309,7 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB142" t="n">
         <v>5</v>
@@ -19332,7 +19332,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Aquisição de Imóveis</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -19368,13 +19368,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F143" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G143" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44906100</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -19397,7 +19397,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>50457592.76</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -19406,43 +19406,43 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>40909913.71</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>20385904.54</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>157005102.66</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>118116606.21</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>123556318.6</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>136619198.12</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>166077092</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>171813039</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
         <v>5</v>
@@ -19455,7 +19455,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Aquisição de Imóveis</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -19516,21 +19516,21 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>51115288.3</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -19539,43 +19539,43 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>40909913.71</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>20385904.54</v>
       </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>158978189.3</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>131270517.15</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>136710229.54</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>138592284.76</v>
       </c>
       <c r="V144" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="W144" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="X144" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AB144" t="n">
         <v>5</v>
@@ -19593,22 +19593,22 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>05 - Outras Fontes</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -19654,12 +19654,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -19696,10 +19696,10 @@
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X145" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="Y145" t="n">
         <v>0</v>
@@ -19708,7 +19708,7 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AB145" t="n">
         <v>5</v>
@@ -19726,7 +19726,7 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>05 - Outras Fontes</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
@@ -19736,12 +19736,12 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -19782,21 +19782,21 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>17330633.4</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -19805,43 +19805,43 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>7871540.4</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>166342578.8</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>136889022</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="X146" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="Y146" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AB146" t="n">
         <v>5</v>
@@ -19859,22 +19859,22 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -19929,7 +19929,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>10114210.09</v>
+        <v>17330633.4</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -19938,43 +19938,43 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>4042120.9</v>
+        <v>7871540.4</v>
       </c>
       <c r="P147" t="n">
-        <v>937022.28</v>
+        <v>29453556.8</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>80380048.28</v>
+        <v>166342578.8</v>
       </c>
       <c r="S147" t="n">
-        <v>33050672.28</v>
+        <v>29453556.8</v>
       </c>
       <c r="T147" t="n">
-        <v>33050672.28</v>
+        <v>29453556.8</v>
       </c>
       <c r="U147" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="X147" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="Y147" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Z147" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>82235403</v>
+        <v>141616875</v>
       </c>
       <c r="AB147" t="n">
         <v>5</v>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -20053,16 +20053,16 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>10114210.09</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -20071,43 +20071,43 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>4618120.9</v>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>937022.28</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>80380048.28</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>33050672.28</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>33050672.28</v>
       </c>
       <c r="U148" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="X148" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA148" t="n">
-        <v>2000</v>
+        <v>82235403</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>08 - Recusos Vinculados</t>
+          <t>00 - Tesouro Municipal</t>
         </is>
       </c>
       <c r="AG148" t="inlineStr">
@@ -20135,12 +20135,12 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -20181,30 +20181,30 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -20213,25 +20213,25 @@
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="X149" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y149" t="n">
         <v>0</v>
@@ -20240,7 +20240,7 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -20258,34 +20258,34 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>00 - Tesouro Municipal</t>
+          <t>08 - Recusos Vinculados</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -20299,22 +20299,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F150" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G150" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -20328,16 +20328,16 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>224000</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -20346,25 +20346,25 @@
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U150" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="X150" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y150" t="n">
         <v>0</v>
@@ -20373,7 +20373,7 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AB150" t="n">
         <v>5</v>
@@ -20381,12 +20381,12 @@
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20447,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -20494,10 +20494,10 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X151" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="Y151" t="n">
         <v>0</v>
@@ -20506,7 +20506,7 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AB151" t="n">
         <v>5</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -20565,22 +20565,22 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F152" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G152" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -20627,10 +20627,10 @@
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X152" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="Y152" t="n">
         <v>0</v>
@@ -20639,7 +20639,7 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AB152" t="n">
         <v>5</v>
@@ -20647,12 +20647,12 @@
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -20698,22 +20698,22 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F153" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G153" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -20760,10 +20760,10 @@
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X153" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y153" t="n">
         <v>0</v>
@@ -20772,7 +20772,7 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB153" t="n">
         <v>5</v>
@@ -20780,12 +20780,12 @@
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -20795,17 +20795,17 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>05/03/2026 07:00:37</t>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>
@@ -20851,16 +20851,16 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>18235012.8</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -20869,34 +20869,34 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>13797559.25</v>
+        <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>35448208.44</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>32116802.57</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>33729566.67</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>32379776.46</v>
+        <v>0</v>
       </c>
       <c r="V154" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X154" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="Y154" t="n">
         <v>0</v>
@@ -20905,7 +20905,7 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
         <v>5</v>
@@ -20923,22 +20923,155 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
+          <t>00 - Tesouro Municipal</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>06/03/2026 06:58:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>422</v>
+      </c>
+      <c r="F155" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G155" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>18932600.81</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>15139361.5</v>
+      </c>
+      <c r="P155" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>35842680.4</v>
+      </c>
+      <c r="S155" t="n">
+        <v>32116802.57</v>
+      </c>
+      <c r="T155" t="n">
+        <v>33729566.67</v>
+      </c>
+      <c r="U155" t="n">
+        <v>32774248.42</v>
+      </c>
+      <c r="V155" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="W155" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X155" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
           <t>08 - Recusos Vinculados</t>
         </is>
       </c>
-      <c r="AG154" t="inlineStr">
+      <c r="AG155" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AH154" t="inlineStr">
+      <c r="AH155" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>05/03/2026 07:00:37</t>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>06/03/2026 06:58:12</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2578031.81</v>
+        <v>2686666.1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1844144.91</v>
+        <v>1931102.91</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>15371.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>12902.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>11257.26</v>
       </c>
       <c r="P8" t="n">
         <v>181083.4</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>301272.61</v>
+        <v>492413.32</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>251299.99</v>
+        <v>306462.71</v>
       </c>
       <c r="P10" t="n">
         <v>1195004.56</v>
@@ -1729,10 +1729,10 @@
         <v>12563981.41</v>
       </c>
       <c r="S10" t="n">
-        <v>7724728.83</v>
+        <v>7737273.83</v>
       </c>
       <c r="T10" t="n">
-        <v>7738517.72</v>
+        <v>7751062.72</v>
       </c>
       <c r="U10" t="n">
         <v>11368976.85</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>447765.46</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>434637.68</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>40389.32</v>
-      </c>
       <c r="P19" t="n">
-        <v>2750000</v>
+        <v>2751110</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2926,13 +2926,13 @@
         <v>8440644</v>
       </c>
       <c r="S19" t="n">
-        <v>4773431.1</v>
+        <v>4831031.1</v>
       </c>
       <c r="T19" t="n">
-        <v>4773431.1</v>
+        <v>4831031.1</v>
       </c>
       <c r="U19" t="n">
-        <v>5690644</v>
+        <v>5689534</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1326292.86</v>
+        <v>2677638.29</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>157814.59</v>
+        <v>192286.9</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4114,13 +4114,13 @@
         <v>157814.59</v>
       </c>
       <c r="P28" t="n">
-        <v>202912.04</v>
+        <v>237022.38</v>
       </c>
       <c r="Q28" t="n">
         <v>9180</v>
       </c>
       <c r="R28" t="n">
-        <v>2037299.69</v>
+        <v>2078758.38</v>
       </c>
       <c r="S28" t="n">
         <v>1486549.4</v>
@@ -4129,7 +4129,7 @@
         <v>1599969.13</v>
       </c>
       <c r="U28" t="n">
-        <v>1834387.65</v>
+        <v>1841736</v>
       </c>
       <c r="V28" t="n">
         <v>113419.73</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>377205.83</v>
+        <v>470486.63</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>374845.23</v>
+        <v>376020.72</v>
       </c>
       <c r="P30" t="n">
         <v>3160.42</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>8704.43</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>379194.76</v>
+        <v>729553.4399999999</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>44544.68</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
         <v>44093.28</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>31441.75</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>244900</v>
+        <v>367350</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1201590.23</v>
+        <v>1204995.23</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -13944,7 +13944,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>102275.25</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>1221823</v>
+        <v>2308010.51</v>
       </c>
       <c r="P109" t="n">
         <v>393733.59</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>2028.89</v>
       </c>
       <c r="P113" t="n">
         <v>1802762.74</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>22963.84</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>1576800</v>
+        <v>2366800</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>5027120.48</v>
+        <v>5478096.41</v>
       </c>
       <c r="P118" t="n">
         <v>1425517.51</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>12000</v>
+        <v>14384</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -16356,16 +16356,16 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>88531.96000000001</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="S120" t="n">
-        <v>88531.96000000001</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="T120" t="n">
-        <v>88531.96000000001</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="U120" t="n">
-        <v>88531.96000000001</v>
+        <v>95531.96000000001</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>24906.96</v>
+        <v>25026.76</v>
       </c>
       <c r="P122" t="n">
         <v>743505.8100000001</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17544,7 +17544,7 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -17943,7 +17943,7 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>179.7</v>
       </c>
       <c r="P132" t="n">
         <v>551.08</v>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>40909913.71</v>
+        <v>41531376.54</v>
       </c>
       <c r="P144" t="n">
         <v>20385904.54</v>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>7871540.4</v>
+        <v>10332515.4</v>
       </c>
       <c r="P147" t="n">
         <v>29453556.8</v>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20071,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>4618120.9</v>
+        <v>7138120.9</v>
       </c>
       <c r="P148" t="n">
         <v>937022.28</v>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>
@@ -20993,7 +20993,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>18932600.81</v>
+        <v>20283437.78</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>06/03/2026 06:58:12</t>
+          <t>07/03/2026 06:42:30</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>07/03/2026 06:42:30</t>
+          <t>08/03/2026 06:44:20</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>08/03/2026 06:44:20</t>
+          <t>09/03/2026 07:06:03</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>7231</v>
+        <v>9031</v>
       </c>
       <c r="S6" t="n">
         <v>7231</v>
@@ -1203,7 +1203,7 @@
         <v>7231</v>
       </c>
       <c r="U6" t="n">
-        <v>7231</v>
+        <v>9031</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>492413.32</v>
+        <v>613322.1899999999</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>447765.46</v>
+        <v>458793.75</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>192286.9</v>
+        <v>262897.39</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>470486.63</v>
+        <v>510878.37</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>275797.2</v>
+        <v>278406.06</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>44544.68</v>
+        <v>70621.7</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>15321.64</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1059.33</v>
+        <v>31993.75</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>116985.29</v>
+        <v>145677.24</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>25026.76</v>
+        <v>57051.42</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>40.27</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>179.7</v>
+        <v>36843.87</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>09/03/2026 07:06:03</t>
+          <t>10/03/2026 16:23:04</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>9031</v>
+        <v>10831</v>
       </c>
       <c r="S6" t="n">
         <v>7231</v>
@@ -1203,7 +1203,7 @@
         <v>7231</v>
       </c>
       <c r="U6" t="n">
-        <v>9031</v>
+        <v>10831</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>613322.1899999999</v>
+        <v>614602.84</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>306462.71</v>
+        <v>310759.01</v>
       </c>
       <c r="P10" t="n">
         <v>1195004.56</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1873.93</v>
+        <v>2012.21</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>124658.62</v>
+        <v>256416.04</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>510878.37</v>
+        <v>779275.04</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>275797.2</v>
+        <v>277071.46</v>
       </c>
       <c r="P34" t="n">
         <v>2931914.44</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -13687,7 +13687,7 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>2092306.37</v>
+        <v>2795073.05</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>5478096.41</v>
+        <v>9099111.57</v>
       </c>
       <c r="P118" t="n">
         <v>1425517.51</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>14384</v>
+        <v>43983</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>41531376.54</v>
+        <v>45916680.23</v>
       </c>
       <c r="P144" t="n">
         <v>20385904.54</v>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20062,7 +20062,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>10114210.09</v>
+        <v>10263982.02</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -20071,7 +20071,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>7138120.9</v>
+        <v>9394570.9</v>
       </c>
       <c r="P148" t="n">
         <v>937022.28</v>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>15139361.5</v>
+        <v>16923026.22</v>
       </c>
       <c r="P155" t="n">
         <v>3068431.98</v>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>10/03/2026 16:23:04</t>
+          <t>11/03/2026 06:58:31</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1188,13 +1188,13 @@
         <v>7231</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>10831</v>
+        <v>21551</v>
       </c>
       <c r="S6" t="n">
         <v>7231</v>
@@ -1203,7 +1203,7 @@
         <v>7231</v>
       </c>
       <c r="U6" t="n">
-        <v>10831</v>
+        <v>14351</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>133308.41</v>
+        <v>133597.18</v>
       </c>
       <c r="S7" t="n">
         <v>5651</v>
@@ -1336,7 +1336,7 @@
         <v>5651</v>
       </c>
       <c r="U7" t="n">
-        <v>133308.41</v>
+        <v>133597.18</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>33633.63</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>614602.84</v>
+        <v>752866.92</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>310759.01</v>
+        <v>313817.61</v>
       </c>
       <c r="P10" t="n">
         <v>1195004.56</v>
@@ -1726,16 +1726,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12563981.41</v>
+        <v>12703981.41</v>
       </c>
       <c r="S10" t="n">
-        <v>7737273.83</v>
+        <v>7837273.83</v>
       </c>
       <c r="T10" t="n">
-        <v>7751062.72</v>
+        <v>7851062.72</v>
       </c>
       <c r="U10" t="n">
-        <v>11368976.85</v>
+        <v>11508976.85</v>
       </c>
       <c r="V10" t="n">
         <v>13788.89</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>13158.64</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>262897.39</v>
+        <v>275322.91</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4123,10 +4123,10 @@
         <v>2078758.38</v>
       </c>
       <c r="S28" t="n">
-        <v>1486549.4</v>
+        <v>1551435.74</v>
       </c>
       <c r="T28" t="n">
-        <v>1599969.13</v>
+        <v>1664855.47</v>
       </c>
       <c r="U28" t="n">
         <v>1841736</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>438842.16</v>
       </c>
       <c r="P29" t="n">
         <v>2164954.67</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>779275.04</v>
+        <v>1142965.11</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>278406.06</v>
+        <v>280470.23</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>964724</v>
+        <v>773543</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5607,10 +5607,10 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>191181</v>
       </c>
       <c r="AA39" t="n">
-        <v>964724</v>
+        <v>773543</v>
       </c>
       <c r="AB39" t="n">
         <v>5</v>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>70621.7</v>
+        <v>139955.33</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2034382.45</v>
+        <v>2870692.14</v>
       </c>
       <c r="P47" t="n">
         <v>4140329.7</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>22178.9</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>245581.64</v>
+        <v>477352.94</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>15321.64</v>
+        <v>15390.74</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>6526.27</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -13687,7 +13687,7 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>2795073.05</v>
+        <v>3487177.25</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14086,7 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>1308418.2</v>
+        <v>2080380.53</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14219,7 +14219,7 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>6526.27</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>28705.17</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>31993.75</v>
+        <v>32062.85</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -14485,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>1059.33</v>
       </c>
       <c r="P106" t="n">
         <v>217702.09</v>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>145677.24</v>
+        <v>189197.21</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -15416,7 +15416,7 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>2028.89</v>
+        <v>2985.29</v>
       </c>
       <c r="P113" t="n">
         <v>1802762.74</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16480,7 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>84841.47</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>57051.42</v>
+        <v>81950.06</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>36843.87</v>
+        <v>36878.42</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19007,7 +19007,7 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>6470104.18</v>
+        <v>9705156.27</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19530,7 +19530,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>51115288.3</v>
+        <v>51898215.71</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -19539,7 +19539,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>45916680.23</v>
+        <v>47169782.59</v>
       </c>
       <c r="P144" t="n">
         <v>20385904.54</v>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>10332515.4</v>
+        <v>12793490.4</v>
       </c>
       <c r="P147" t="n">
         <v>29453556.8</v>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20071,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>9394570.9</v>
+        <v>9545118.99</v>
       </c>
       <c r="P148" t="n">
         <v>937022.28</v>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>11/03/2026 06:58:31</t>
+          <t>12/03/2026 07:01:52</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2686666.1</v>
+        <v>2809167.78</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4984.15</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1330,13 +1330,13 @@
         <v>133597.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5651</v>
+        <v>17143.8</v>
       </c>
       <c r="T7" t="n">
-        <v>5651</v>
+        <v>17143.8</v>
       </c>
       <c r="U7" t="n">
-        <v>133597.18</v>
+        <v>128613.03</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2012.21</v>
+        <v>2689.09</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2777.76</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2777.76</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>438842.16</v>
+        <v>448751.2</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>280470.23</v>
+        <v>280924.77</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
         <v>186346</v>
       </c>
       <c r="R43" t="n">
-        <v>3775528.66</v>
+        <v>3780081.94</v>
       </c>
       <c r="S43" t="n">
         <v>3160777.22</v>
@@ -6124,7 +6124,7 @@
         <v>3160777.22</v>
       </c>
       <c r="U43" t="n">
-        <v>3775528.66</v>
+        <v>3780081.94</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>9909.040000000001</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1201590.23</v>
+        <v>1204995.23</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -13956,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>7692964.08</v>
+        <v>7742964.08</v>
       </c>
       <c r="S102" t="n">
         <v>739539.62</v>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>540.3099999999999</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -14896,10 +14896,10 @@
         <v>5281025.59</v>
       </c>
       <c r="S109" t="n">
-        <v>4493558.41</v>
+        <v>4887292</v>
       </c>
       <c r="T109" t="n">
-        <v>4887292</v>
+        <v>5281025.59</v>
       </c>
       <c r="U109" t="n">
         <v>4887292</v>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>2985.29</v>
+        <v>116985.29</v>
       </c>
       <c r="P113" t="n">
         <v>1802762.74</v>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>43983</v>
+        <v>62133</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>84841.47</v>
+        <v>94750.50999999999</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>47169782.59</v>
+        <v>50457592.76</v>
       </c>
       <c r="P144" t="n">
         <v>20385904.54</v>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20071,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>9545118.99</v>
+        <v>10114210.09</v>
       </c>
       <c r="P148" t="n">
         <v>937022.28</v>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>16923026.22</v>
+        <v>17479270.29</v>
       </c>
       <c r="P155" t="n">
         <v>3068431.98</v>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>12/03/2026 07:01:52</t>
+          <t>13/03/2026 06:55:07</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1931102.91</v>
+        <v>2686666.1</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>752866.92</v>
+        <v>784883.1800000001</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1717,10 +1717,10 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>313817.61</v>
+        <v>302762.11</v>
       </c>
       <c r="P10" t="n">
-        <v>1195004.56</v>
+        <v>1207154.56</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>12703981.41</v>
       </c>
       <c r="S10" t="n">
-        <v>7837273.83</v>
+        <v>7840381.78</v>
       </c>
       <c r="T10" t="n">
-        <v>7851062.72</v>
+        <v>7866320.67</v>
       </c>
       <c r="U10" t="n">
-        <v>11508976.85</v>
+        <v>11496826.85</v>
       </c>
       <c r="V10" t="n">
-        <v>13788.89</v>
+        <v>25938.89</v>
       </c>
       <c r="W10" t="n">
         <v>12568415</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>458793.75</v>
+        <v>459960.41</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>434637.68</v>
+        <v>447765.46</v>
       </c>
       <c r="P19" t="n">
         <v>2751110</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>275322.91</v>
+        <v>316750.16</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4111,16 +4111,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>157814.59</v>
+        <v>158063.21</v>
       </c>
       <c r="P28" t="n">
-        <v>237022.38</v>
+        <v>237557.39</v>
       </c>
       <c r="Q28" t="n">
         <v>9180</v>
       </c>
       <c r="R28" t="n">
-        <v>2078758.38</v>
+        <v>2079293.39</v>
       </c>
       <c r="S28" t="n">
         <v>1551435.74</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1142965.11</v>
+        <v>1150861.71</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>376020.72</v>
+        <v>469617.63</v>
       </c>
       <c r="P30" t="n">
         <v>3160.42</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>8704.43</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>280924.77</v>
+        <v>281090.39</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>277071.46</v>
+        <v>280788.66</v>
       </c>
       <c r="P34" t="n">
         <v>2931914.44</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>139955.33</v>
+        <v>175233.56</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>44093.28</v>
+        <v>44544.68</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         <v>186346</v>
       </c>
       <c r="R43" t="n">
-        <v>3780081.94</v>
+        <v>15139782.73</v>
       </c>
       <c r="S43" t="n">
         <v>3160777.22</v>
@@ -6124,7 +6124,7 @@
         <v>3160777.22</v>
       </c>
       <c r="U43" t="n">
-        <v>3780081.94</v>
+        <v>15139782.73</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>9909.040000000001</v>
+        <v>40961.43</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10495,7 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -10906,10 +10906,10 @@
         <v>416595.36</v>
       </c>
       <c r="S79" t="n">
-        <v>339609.47</v>
+        <v>363452.83</v>
       </c>
       <c r="T79" t="n">
-        <v>339609.47</v>
+        <v>363452.83</v>
       </c>
       <c r="U79" t="n">
         <v>392752</v>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1204995.23</v>
+        <v>2358168.48</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>102275.25</v>
       </c>
       <c r="P102" t="n">
         <v>50000</v>
@@ -13965,10 +13965,10 @@
         <v>7742964.08</v>
       </c>
       <c r="S102" t="n">
-        <v>739539.62</v>
+        <v>771564.08</v>
       </c>
       <c r="T102" t="n">
-        <v>739539.62</v>
+        <v>771564.08</v>
       </c>
       <c r="U102" t="n">
         <v>7692964.08</v>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>80987.12</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>9099111.57</v>
+        <v>9425812.26</v>
       </c>
       <c r="P118" t="n">
         <v>1425517.51</v>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>11112.8</v>
+        <v>22225.6</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>81950.06</v>
+        <v>82069.86</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -16622,7 +16622,7 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3258804.45</v>
+        <v>3708073.53</v>
       </c>
       <c r="S122" t="n">
         <v>1959433.84</v>
@@ -16631,7 +16631,7 @@
         <v>1959433.84</v>
       </c>
       <c r="U122" t="n">
-        <v>2515298.64</v>
+        <v>2964567.72</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16870,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1967.85</v>
+        <v>3935.7</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>36878.42</v>
+        <v>37058.12</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -17955,10 +17955,10 @@
         <v>5032621.72</v>
       </c>
       <c r="S132" t="n">
-        <v>551310.86</v>
+        <v>570925.76</v>
       </c>
       <c r="T132" t="n">
-        <v>551310.86</v>
+        <v>570925.76</v>
       </c>
       <c r="U132" t="n">
         <v>5032070.64</v>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>50457592.76</v>
+        <v>51115288.3</v>
       </c>
       <c r="P144" t="n">
         <v>20385904.54</v>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -19950,10 +19950,10 @@
         <v>166342578.8</v>
       </c>
       <c r="S147" t="n">
-        <v>29453556.8</v>
+        <v>105672056.8</v>
       </c>
       <c r="T147" t="n">
-        <v>29453556.8</v>
+        <v>105672056.8</v>
       </c>
       <c r="U147" t="n">
         <v>136889022</v>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20074,13 +20074,13 @@
         <v>10114210.09</v>
       </c>
       <c r="P148" t="n">
-        <v>937022.28</v>
+        <v>1821463.91</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>80380048.28</v>
+        <v>81264489.91</v>
       </c>
       <c r="S148" t="n">
         <v>33050672.28</v>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>
@@ -20993,16 +20993,16 @@
         </is>
       </c>
       <c r="L155" t="n">
+        <v>20378876.76</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
         <v>20283437.78</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0</v>
-      </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" t="n">
-        <v>17479270.29</v>
       </c>
       <c r="P155" t="n">
         <v>3068431.98</v>
@@ -21011,7 +21011,7 @@
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>35842680.4</v>
+        <v>36614750.58</v>
       </c>
       <c r="S155" t="n">
         <v>32116802.57</v>
@@ -21020,7 +21020,7 @@
         <v>33729566.67</v>
       </c>
       <c r="U155" t="n">
-        <v>32774248.42</v>
+        <v>33546318.6</v>
       </c>
       <c r="V155" t="n">
         <v>1612764.1</v>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>13/03/2026 06:55:07</t>
+          <t>14/03/2026 06:49:08</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>14/03/2026 06:49:08</t>
+          <t>15/03/2026 06:48:05</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>15/03/2026 06:48:05</t>
+          <t>16/03/2026 07:18:23</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202603.xlsx
+++ b/base_despesas/2026/despesas_202603.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>800141.13</v>
+        <v>821107.3</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>302762.11</v>
+        <v>416459.1</v>
       </c>
       <c r="P10" t="n">
         <v>1207154.56</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>124658.62</v>
+        <v>256416.04</v>
       </c>
       <c r="P17" t="n">
         <v>14849.99</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>467980.34</v>
+        <v>925027.92</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>447765.46</v>
+        <v>458793.75</v>
       </c>
       <c r="P19" t="n">
         <v>2751110</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>332534.87</v>
+        <v>334097.91</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>158063.21</v>
+        <v>158216.99</v>
       </c>
       <c r="P28" t="n">
         <v>237557.39</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1150861.71</v>
+        <v>1151595.62</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4377,16 +4377,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>469617.63</v>
+        <v>511123.68</v>
       </c>
       <c r="P30" t="n">
-        <v>3160.42</v>
+        <v>636049.5600000001</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>17193479.55</v>
+        <v>18461792.37</v>
       </c>
       <c r="S30" t="n">
         <v>16777679.95</v>
@@ -4395,7 +4395,7 @@
         <v>16784252.6</v>
       </c>
       <c r="U30" t="n">
-        <v>17190319.13</v>
+        <v>17825742.81</v>
       </c>
       <c r="V30" t="n">
         <v>6572.65</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>38322.58</v>
+        <v>62097.08</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>425800.27</v>
+        <v>428314.07</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>44544.68</v>
+        <v>70621.7</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>680791.95</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>15390.74</v>
+        <v>15459.84</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -9963,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>15321.64</v>
       </c>
       <c r="P72" t="n">
         <v>1495.27</v>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>32062.85</v>
+        <v>33191.28</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -14618,7 +14618,7 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>1059.33</v>
+        <v>31993.75</v>
       </c>
       <c r="P107" t="n">
         <v>217702.09</v>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>230113.37</v>
+        <v>233314.85</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -15549,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>116985.29</v>
+        <v>145677.24</v>
       </c>
       <c r="P114" t="n">
         <v>1802762.74</v>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>161011.3</v>
+        <v>181137.08</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -16746,7 +16746,7 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>25026.76</v>
+        <v>51797.82</v>
       </c>
       <c r="P123" t="n">
         <v>743505.8100000001</v>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>73722.28999999999</v>
+        <v>73756.84</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>179.7</v>
+        <v>36843.87</v>
       </c>
       <c r="P133" t="n">
         <v>551.08</v>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -19548,7 +19548,7 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -19557,7 +19557,7 @@
         <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>361510</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -19675,7 +19675,7 @@
         <v>51115288.3</v>
       </c>
       <c r="P145" t="n">
-        <v>20385904.54</v>
+        <v>21043600.09</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
@@ -19684,13 +19684,13 @@
         <v>158978189.3</v>
       </c>
       <c r="S145" t="n">
-        <v>131270517.15</v>
+        <v>133293603.78</v>
       </c>
       <c r="T145" t="n">
-        <v>136710229.54</v>
+        <v>138733316.17</v>
       </c>
       <c r="U145" t="n">
-        <v>138592284.76</v>
+        <v>137934589.21</v>
       </c>
       <c r="V145" t="n">
         <v>5439712.39</v>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20062,7 +20062,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>19285095</v>
+        <v>20262325.8</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -20074,13 +20074,13 @@
         <v>12793490.4</v>
       </c>
       <c r="P148" t="n">
-        <v>29453556.8</v>
+        <v>60670522</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>166342578.8</v>
+        <v>197559544</v>
       </c>
       <c r="S148" t="n">
         <v>105672056.8</v>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20195,7 +20195,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>10450648.71</v>
+        <v>10603331.24</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
@@ -21144,7 +21144,7 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>36908064.03</v>
+        <v>37604582.77</v>
       </c>
       <c r="S156" t="n">
         <v>32116802.57</v>
@@ -21153,7 +21153,7 @@
         <v>33729566.67</v>
       </c>
       <c r="U156" t="n">
-        <v>33839632.05</v>
+        <v>34536150.79</v>
       </c>
       <c r="V156" t="n">
         <v>1612764.1</v>
@@ -21204,7 +21204,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>17/03/2026 10:05:39</t>
+          <t>18/03/2026 07:11:17</t>
         </is>
       </c>
     </row>
